--- a/parent_feedback_forms/008_education_parent_opinion_information_collection_form--parent_feedback_forms.xlsx
+++ b/parent_feedback_forms/008_education_parent_opinion_information_collection_form--parent_feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -964,8 +964,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -993,12 +993,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'very_unsatisfied'}</t>
+          <t>very_unsatisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Very Unsatisfied'}</t>
+          <t>Very Unsatisfied</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'unsatisfied'}</t>
+          <t>unsatisfied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Unsatisfied'}</t>
+          <t>Unsatisfied</t>
         </is>
       </c>
     </row>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'satisfied'}</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Satisfied'}</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Very Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'very_unsatisfied'}</t>
+          <t>very_unsatisfied</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Very Unsatisfied'}</t>
+          <t>Very Unsatisfied</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'unsatisfied'}</t>
+          <t>unsatisfied</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Unsatisfied'}</t>
+          <t>Unsatisfied</t>
         </is>
       </c>
     </row>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'satisfied'}</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Satisfied'}</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Very Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -1163,12 +1163,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'very_rarely'}</t>
+          <t>very_rarely</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Very Rarely'}</t>
+          <t>Very Rarely</t>
         </is>
       </c>
     </row>
@@ -1180,12 +1180,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1197,12 +1197,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'often'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Often'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
@@ -1231,12 +1231,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'very_often'}</t>
+          <t>very_often</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Very Often'}</t>
+          <t>Very Often</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'very_often'}</t>
+          <t>very_often</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Very Often'}</t>
+          <t>Very Often</t>
         </is>
       </c>
     </row>
@@ -1265,12 +1265,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'often'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Often'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
@@ -1282,12 +1282,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'seldom'}</t>
+          <t>seldom</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Seldom'}</t>
+          <t>Seldom</t>
         </is>
       </c>
     </row>
@@ -1316,12 +1316,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1333,12 +1333,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Very Dissatisfied'}</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1350,12 +1350,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'dissatisfied'}</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Dissatisfied'}</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1367,12 +1367,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1384,12 +1384,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'satisfied'}</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Satisfied'}</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
@@ -1401,12 +1401,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Very Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'grade_1'}</t>
+          <t>grade_1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Grade 1'}</t>
+          <t>Grade 1</t>
         </is>
       </c>
     </row>
@@ -1435,12 +1435,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'grade_2'}</t>
+          <t>grade_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Grade 2'}</t>
+          <t>Grade 2</t>
         </is>
       </c>
     </row>
@@ -1452,12 +1452,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'grade_3'}</t>
+          <t>grade_3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Grade 3'}</t>
+          <t>Grade 3</t>
         </is>
       </c>
     </row>
@@ -1469,12 +1469,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'grade_4'}</t>
+          <t>grade_4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Grade 4'}</t>
+          <t>Grade 4</t>
         </is>
       </c>
     </row>
@@ -1486,12 +1486,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'grade_5'}</t>
+          <t>grade_5</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Grade 5'}</t>
+          <t>Grade 5</t>
         </is>
       </c>
     </row>
@@ -1503,12 +1503,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'grade_6'}</t>
+          <t>grade_6</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Grade 6'}</t>
+          <t>Grade 6</t>
         </is>
       </c>
     </row>
@@ -1520,12 +1520,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'grade_7'}</t>
+          <t>grade_7</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Grade 7'}</t>
+          <t>Grade 7</t>
         </is>
       </c>
     </row>
@@ -1537,12 +1537,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'grade_8'}</t>
+          <t>grade_8</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Grade 8'}</t>
+          <t>Grade 8</t>
         </is>
       </c>
     </row>
@@ -1554,12 +1554,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'grade_9'}</t>
+          <t>grade_9</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'Grade 9'}</t>
+          <t>Grade 9</t>
         </is>
       </c>
     </row>
@@ -1571,12 +1571,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'grade_10'}</t>
+          <t>grade_10</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'Grade 10'}</t>
+          <t>Grade 10</t>
         </is>
       </c>
     </row>
@@ -1588,12 +1588,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'a'}</t>
+          <t>a</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'A'}</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -1605,12 +1605,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'b'}</t>
+          <t>b</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'B'}</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -1622,12 +1622,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'c'}</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'C'}</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'d'}</t>
+          <t>d</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 'D'}</t>
+          <t>D</t>
         </is>
       </c>
     </row>
@@ -1656,12 +1656,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'label':_'e'}</t>
+          <t>e</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'label': 'E'}</t>
+          <t>E</t>
         </is>
       </c>
     </row>
@@ -1673,12 +1673,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'label':_'parent'}</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'label': 'Parent'}</t>
+          <t>Parent</t>
         </is>
       </c>
     </row>
@@ -1690,12 +1690,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'label':_'teacher'}</t>
+          <t>teacher</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'label': 'Teacher'}</t>
+          <t>Teacher</t>
         </is>
       </c>
     </row>
@@ -1707,12 +1707,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'label':_'school_admin'}</t>
+          <t>school_admin</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'label': 'School Admin'}</t>
+          <t>School Admin</t>
         </is>
       </c>
     </row>
@@ -1724,12 +1724,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1741,12 +1741,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'label':_'very_rarely'}</t>
+          <t>very_rarely</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'label': 'Very Rarely'}</t>
+          <t>Very Rarely</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1775,12 +1775,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1792,12 +1792,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'label':_'often'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'label': 'Often'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
@@ -1809,12 +1809,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'label':_'very_often'}</t>
+          <t>very_often</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'label': 'Very Often'}</t>
+          <t>Very Often</t>
         </is>
       </c>
     </row>
@@ -1826,12 +1826,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'label':_'very_unimportant'}</t>
+          <t>very_unimportant</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'label': 'Very Unimportant'}</t>
+          <t>Very Unimportant</t>
         </is>
       </c>
     </row>
@@ -1843,12 +1843,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'label':_'unimportant'}</t>
+          <t>unimportant</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'label': 'Unimportant'}</t>
+          <t>Unimportant</t>
         </is>
       </c>
     </row>
@@ -1860,12 +1860,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1877,12 +1877,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'label':_'important'}</t>
+          <t>important</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'label': 'Important'}</t>
+          <t>Important</t>
         </is>
       </c>
     </row>
@@ -1894,12 +1894,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'label':_'very_important'}</t>
+          <t>very_important</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'label': 'Very Important'}</t>
+          <t>Very Important</t>
         </is>
       </c>
     </row>
@@ -1911,12 +1911,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'label':_'very_unsatisfied'}</t>
+          <t>very_unsatisfied</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'label': 'Very Unsatisfied'}</t>
+          <t>Very Unsatisfied</t>
         </is>
       </c>
     </row>
@@ -1928,12 +1928,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'label':_'unsatisfied'}</t>
+          <t>unsatisfied</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'label': 'Unsatisfied'}</t>
+          <t>Unsatisfied</t>
         </is>
       </c>
     </row>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1962,12 +1962,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'label':_'satisfied'}</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'label': 'Satisfied'}</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
@@ -1979,12 +1979,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'label': 'Very Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
